--- a/提交/结果文件/结果提交表.xlsx
+++ b/提交/结果文件/结果提交表.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Q1_单点组批" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Q2_运输架次" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Q2_逐箱交付" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Q3_中继架次" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Q3_通信保障" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Q4_分区配置" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q1_单点组批" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q2_运输架次" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q2_逐箱交付" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_中继架次" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_通信保障" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_分区配置" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4463,16 +4463,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14317.7</v>
+        <v>14326.9</v>
       </c>
       <c r="E7" t="n">
-        <v>109.244278</v>
+        <v>109.241278</v>
       </c>
       <c r="F7" t="n">
-        <v>23.002389</v>
+        <v>23.000889</v>
       </c>
       <c r="G7" t="n">
-        <v>425.32</v>
+        <v>438.04</v>
       </c>
       <c r="H7" t="n">
         <v>14680.5</v>
@@ -4481,10 +4481,10 @@
         <v>15372.8</v>
       </c>
       <c r="J7" t="n">
-        <v>15542.5</v>
+        <v>15533.9</v>
       </c>
       <c r="K7" t="n">
-        <v>0.294854</v>
+        <v>0.288325</v>
       </c>
     </row>
     <row r="8">
@@ -4586,16 +4586,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>21762.4</v>
+        <v>21771.2</v>
       </c>
       <c r="E10" t="n">
-        <v>109.247278</v>
+        <v>109.245778</v>
       </c>
       <c r="F10" t="n">
         <v>22.999389</v>
       </c>
       <c r="G10" t="n">
-        <v>490.89</v>
+        <v>486.98</v>
       </c>
       <c r="H10" t="n">
         <v>22171.2</v>
@@ -4604,10 +4604,10 @@
         <v>22735.8</v>
       </c>
       <c r="J10" t="n">
-        <v>22957.3</v>
+        <v>22948.3</v>
       </c>
       <c r="K10" t="n">
-        <v>0.28034</v>
+        <v>0.274735</v>
       </c>
     </row>
     <row r="11">
@@ -4709,16 +4709,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>27941.2</v>
+        <v>27941.1</v>
       </c>
       <c r="E13" t="n">
-        <v>109.238278</v>
+        <v>109.236778</v>
       </c>
       <c r="F13" t="n">
         <v>22.984389</v>
       </c>
       <c r="G13" t="n">
-        <v>608.17</v>
+        <v>618.59</v>
       </c>
       <c r="H13" t="n">
         <v>28432.3</v>
@@ -4727,10 +4727,10 @@
         <v>28875</v>
       </c>
       <c r="J13" t="n">
-        <v>29187.9</v>
+        <v>29188.8</v>
       </c>
       <c r="K13" t="n">
-        <v>0.287941</v>
+        <v>0.287251</v>
       </c>
     </row>
     <row r="14">
